--- a/api/game_conf/excel/Index.xlsx
+++ b/api/game_conf/excel/Index.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,13 +444,11 @@
           <t>类型表</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>game_attribute.xlsx</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>游戏字段</t>
@@ -463,13 +461,11 @@
           <t>类型表</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>game_enumeration.xlsx</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>游戏枚举</t>
@@ -492,7 +488,6 @@
           <t>battle.xlsx</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>战斗规则</t>
@@ -515,7 +510,6 @@
           <t>formation.xlsx</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>编队配置</t>
@@ -538,7 +532,6 @@
           <t>troop.xlsx</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>兵种配置</t>
@@ -561,7 +554,6 @@
           <t>hero.xlsx</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>英雄系统配置</t>
@@ -584,7 +576,6 @@
           <t>hero_exp.xlsx</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>英雄升级经验</t>
@@ -607,7 +598,6 @@
           <t>hero_attr.xlsx</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>英雄属性</t>
@@ -622,18 +612,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>hero_base</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>item.xlsx</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>hero_base.xlsx</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>道具配置</t>
+          <t>英雄基础信息</t>
         </is>
       </c>
     </row>
@@ -645,18 +634,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>exchange</t>
+          <t>hero_method</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>exchange.xlsx</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>hero_method.xlsx</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>货币兑换</t>
+          <t>战法配置</t>
         </is>
       </c>
     </row>
@@ -668,18 +656,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>resource</t>
+          <t>hero_method_slot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>resource.xlsx</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>hero_method_slot.xlsx</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>资源地产量</t>
+          <t>英雄战法槽位</t>
         </is>
       </c>
     </row>
@@ -691,18 +678,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gacha_pool</t>
+          <t>hero_policy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gacha_pool.xlsx</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>hero_policy.xlsx</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>抽卡池</t>
+          <t>政策配置</t>
         </is>
       </c>
     </row>
@@ -714,18 +700,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gacha_drop_group</t>
+          <t>hero_group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gacha_drop_group.xlsx</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>hero_group.xlsx</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>抽卡掉落组</t>
+          <t>羁绊配置</t>
         </is>
       </c>
     </row>
@@ -737,18 +722,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gacha_drop_item</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gacha_drop_item.xlsx</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>item.xlsx</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>抽卡掉落条目</t>
+          <t>道具配置</t>
         </is>
       </c>
     </row>
@@ -760,18 +744,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>guard.xlsx</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>exchange.xlsx</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>守军配置</t>
+          <t>货币兑换</t>
         </is>
       </c>
     </row>
@@ -783,18 +766,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>guard_config</t>
+          <t>resource</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>guard_config.xlsx</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>resource.xlsx</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>守军等级配置</t>
+          <t>资源地产量</t>
         </is>
       </c>
     </row>
@@ -806,18 +788,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>guard_slot</t>
+          <t>gacha_pool</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>guard_slot.xlsx</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>gacha_pool.xlsx</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>守军槽位</t>
+          <t>抽卡池</t>
         </is>
       </c>
     </row>
@@ -829,18 +810,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>soldier</t>
+          <t>gacha_drop_group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>soldier.xlsx</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>gacha_drop_group.xlsx</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>兵力配置</t>
+          <t>抽卡掉落组</t>
         </is>
       </c>
     </row>
@@ -852,18 +832,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>soldier_hero_cap</t>
+          <t>gacha_drop_item</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>soldier_hero_cap.xlsx</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>gacha_drop_item.xlsx</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>英雄等级兵力断点</t>
+          <t>抽卡掉落条目</t>
         </is>
       </c>
     </row>
@@ -875,18 +854,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>soldier_barrack_bonus</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>soldier_barrack_bonus.xlsx</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>guard.xlsx</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>兵营等级兵力加成断点</t>
+          <t>守军配置</t>
         </is>
       </c>
     </row>
@@ -898,18 +876,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>guard_config</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>review.xlsx</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>guard_config.xlsx</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>审查玩法配置</t>
+          <t>守军等级配置</t>
         </is>
       </c>
     </row>
@@ -921,18 +898,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>review_level</t>
+          <t>guard_slot</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>review_level.xlsx</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>guard_slot.xlsx</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>审查等级</t>
+          <t>守军槽位</t>
         </is>
       </c>
     </row>
@@ -944,18 +920,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>soldier</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>skill.xlsx</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>soldier.xlsx</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>技能配置</t>
+          <t>兵力配置</t>
         </is>
       </c>
     </row>
@@ -967,18 +942,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>skill_collection</t>
+          <t>soldier_hero_cap</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>skill_collection.xlsx</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>soldier_hero_cap.xlsx</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>技能收藏</t>
+          <t>英雄等级兵力断点</t>
         </is>
       </c>
     </row>
@@ -990,18 +964,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>skill_setting</t>
+          <t>soldier_barrack_bonus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>skill_setting.xlsx</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>soldier_barrack_bonus.xlsx</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>技能槽位配置</t>
+          <t>兵营等级兵力加成断点</t>
         </is>
       </c>
     </row>
@@ -1013,16 +986,125 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>review.xlsx</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>审查玩法配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>数据表</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>review_level</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>review_level.xlsx</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>审查等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>数据表</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>skill.xlsx</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>技能配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>数据表</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>skill_collection</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>skill_collection.xlsx</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>技能收藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>数据表</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>skill_setting</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>skill_setting.xlsx</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>技能槽位配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>数据表</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>building</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>building.xlsx</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>建筑配置</t>
         </is>
